--- a/Absen/6. Mei 2026 - TARBIYAH & DAKWAH DT-R.xlsx
+++ b/Absen/6. Mei 2026 - TARBIYAH & DAKWAH DT-R.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pengajian\Absen\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ASATIDZ\Zen\pengajian-baru\Absen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2098FC0F-F32C-4BD1-A787-03E1E9D6B2C7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{136CF72B-6F18-4FDA-BB91-72F83CF358DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="37635" windowHeight="21840" xr2:uid="{2E39FF77-035B-4F7C-ACEB-1A442C392774}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2E39FF77-035B-4F7C-ACEB-1A442C392774}"/>
   </bookViews>
   <sheets>
     <sheet name="TARBIYAH" sheetId="2" r:id="rId1"/>
@@ -24,7 +24,12 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -32,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="72">
   <si>
     <t>NAMA</t>
   </si>
@@ -218,9 +223,6 @@
 Terima kasih…</t>
   </si>
   <si>
-    <t>1 Mei 2026</t>
-  </si>
-  <si>
     <t>: MEI 2026</t>
   </si>
   <si>
@@ -228,6 +230,33 @@
   </si>
   <si>
     <t>Sakit</t>
+  </si>
+  <si>
+    <t>15 Mei 2026</t>
+  </si>
+  <si>
+    <t>22 Mei 2026</t>
+  </si>
+  <si>
+    <t>Di luar kota</t>
+  </si>
+  <si>
+    <t>Tugas</t>
+  </si>
+  <si>
+    <t>Di rumah mertua</t>
+  </si>
+  <si>
+    <t>Badal di RI</t>
+  </si>
+  <si>
+    <t>Di kantor</t>
+  </si>
+  <si>
+    <t>Masih kerja</t>
+  </si>
+  <si>
+    <t>Tanpa keterangan</t>
   </si>
 </sst>
 </file>
@@ -618,7 +647,17 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="10">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -769,36 +808,6 @@
         <scheme val="major"/>
       </font>
     </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -830,31 +839,31 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{50CAA0CF-06E4-471A-8CAA-E0E3D0553E02}" name="Table1" displayName="Table1" ref="M10:N21" totalsRowShown="0" headerRowDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{50CAA0CF-06E4-471A-8CAA-E0E3D0553E02}" name="Table1" displayName="Table1" ref="M10:N21" totalsRowShown="0" headerRowDxfId="9">
   <autoFilter ref="M10:N21" xr:uid="{50CAA0CF-06E4-471A-8CAA-E0E3D0553E02}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{7BD02032-E365-49A8-ADAB-44D6FB3AFCD1}" name="Nama" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{41948D79-27FC-4502-92CC-571E48B0487D}" name="Nomor WA" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{7BD02032-E365-49A8-ADAB-44D6FB3AFCD1}" name="Nama" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{41948D79-27FC-4502-92CC-571E48B0487D}" name="Nomor WA" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{11B7F338-C63F-40E2-80FF-0AC823156E9D}" name="Table2" displayName="Table2" ref="P26:Q27" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{11B7F338-C63F-40E2-80FF-0AC823156E9D}" name="Table2" displayName="Table2" ref="P26:Q27" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <autoFilter ref="P26:Q27" xr:uid="{11B7F338-C63F-40E2-80FF-0AC823156E9D}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{84005749-F834-45CA-94CD-2EDD5B1E1F63}" name="Teks WA 1" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{29720DB4-DB3A-41BE-9B35-9301A3705ADA}" name="Teks WA 2" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{84005749-F834-45CA-94CD-2EDD5B1E1F63}" name="Teks WA 1" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{29720DB4-DB3A-41BE-9B35-9301A3705ADA}" name="Teks WA 2" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -892,7 +901,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -998,7 +1007,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1140,7 +1149,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1233,7 +1242,7 @@
         <v>21</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
@@ -1307,7 +1316,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F10" s="18" t="b">
         <v>1</v>
@@ -1425,7 +1434,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E13" s="10"/>
+      <c r="E13" s="10" t="s">
+        <v>67</v>
+      </c>
       <c r="F13" s="18" t="b">
         <v>0</v>
       </c>
@@ -1433,7 +1444,9 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H13" s="11"/>
+      <c r="H13" s="10" t="s">
+        <v>65</v>
+      </c>
       <c r="L13" s="3"/>
       <c r="M13" s="1" t="s">
         <v>45</v>
@@ -1443,7 +1456,7 @@
       </c>
       <c r="P13" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>https://wa.me/6282320040021?text=Assalamualaikum%20Mas%20Aswan%0A%0ASaya%20mau%20minta%20keterangannya%20untuk%20ketidakhadiran%20pengajian%20tanggal%201%20Mei%202026%20dan%20tanggal%201%20Mei%202026%0A%0ATerima%20kasih%E2%80%A6</v>
+        <v/>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
@@ -1502,7 +1515,9 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H15" s="10"/>
+      <c r="H15" s="10" t="s">
+        <v>69</v>
+      </c>
       <c r="M15" s="1" t="s">
         <v>47</v>
       </c>
@@ -1511,7 +1526,7 @@
       </c>
       <c r="P15" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>https://wa.me/6281347471525?text=Assalamualaikum%20Pak%20Mamat%0A%0ASaya%20mau%20minta%20keterangannya%20untuk%20ketidakhadiran%20pengajian%20tanggal%201%20Mei%202026%0A%0ATerima%20kasih%E2%80%A6</v>
+        <v/>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
@@ -1545,7 +1560,7 @@
       </c>
       <c r="P16" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>https://wa.me/6285255990709?text=Assalamualaikum%20Mas%20Firman%0A%0ASaya%20mau%20minta%20keterangannya%20untuk%20ketidakhadiran%20pengajian%20tanggal%201%20Mei%202026%0A%0ATerima%20kasih%E2%80%A6</v>
+        <v>https://wa.me/6285255990709?text=Assalamualaikum%20Mas%20Firman%0A%0ASaya%20mau%20minta%20keterangannya%20untuk%20ketidakhadiran%20pengajian%20tanggal%2022%20Mei%202026%0A%0ATerima%20kasih%E2%80%A6</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
@@ -1570,7 +1585,9 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H17" s="10"/>
+      <c r="H17" s="10" t="s">
+        <v>70</v>
+      </c>
       <c r="M17" s="1" t="s">
         <v>49</v>
       </c>
@@ -1579,7 +1596,7 @@
       </c>
       <c r="P17" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>https://wa.me/6282124386879?text=Assalamualaikum%20Mas%20Suhud%0A%0ASaya%20mau%20minta%20keterangannya%20untuk%20ketidakhadiran%20pengajian%20tanggal%201%20Mei%202026%0A%0ATerima%20kasih%E2%80%A6</v>
+        <v/>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
@@ -1596,7 +1613,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E18" s="10"/>
+      <c r="E18" s="10" t="s">
+        <v>66</v>
+      </c>
       <c r="F18" s="18" t="b">
         <v>0</v>
       </c>
@@ -1605,7 +1624,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>50</v>
@@ -1615,7 +1634,7 @@
       </c>
       <c r="P18" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>https://wa.me/6282354144365?text=Assalamualaikum%20Mas%20Salman%0A%0ASaya%20mau%20minta%20keterangannya%20untuk%20ketidakhadiran%20pengajian%20tanggal%201%20Mei%202026%0A%0ATerima%20kasih%E2%80%A6</v>
+        <v/>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -1634,13 +1653,15 @@
       </c>
       <c r="E19" s="10"/>
       <c r="F19" s="18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" s="18" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H19" s="11"/>
+        <v>1</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>68</v>
+      </c>
       <c r="M19" s="1" t="s">
         <v>51</v>
       </c>
@@ -1649,7 +1670,7 @@
       </c>
       <c r="P19" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>https://wa.me/6285250888733?text=Assalamualaikum%20Mas%20Reza%0A%0ASaya%20mau%20minta%20keterangannya%20untuk%20ketidakhadiran%20pengajian%20tanggal%201%20Mei%202026%0A%0ATerima%20kasih%E2%80%A6</v>
+        <v/>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -1666,7 +1687,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E20" s="10"/>
+      <c r="E20" s="11" t="s">
+        <v>71</v>
+      </c>
       <c r="F20" s="18" t="b">
         <v>0</v>
       </c>
@@ -1674,7 +1697,9 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H20" s="11"/>
+      <c r="H20" s="11" t="s">
+        <v>71</v>
+      </c>
       <c r="M20" s="1" t="s">
         <v>52</v>
       </c>
@@ -1683,7 +1708,7 @@
       </c>
       <c r="P20" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>https://wa.me/6281220142015?text=Assalamualaikum%20Pak%20Syakur%0A%0ASaya%20mau%20minta%20keterangannya%20untuk%20ketidakhadiran%20pengajian%20tanggal%201%20Mei%202026%20dan%20tanggal%201%20Mei%202026%0A%0ATerima%20kasih%E2%80%A6</v>
+        <v/>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
@@ -1708,7 +1733,9 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H21" s="10"/>
+      <c r="H21" s="10" t="s">
+        <v>62</v>
+      </c>
       <c r="M21" s="1" t="s">
         <v>53</v>
       </c>
@@ -1717,7 +1744,7 @@
       </c>
       <c r="P21" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>https://wa.me/6282229432434?text=Assalamualaikum%20Mas%20Wahap%0A%0ASaya%20mau%20minta%20keterangannya%20untuk%20ketidakhadiran%20pengajian%20tanggal%201%20Mei%202026%0A%0ATerima%20kasih%E2%80%A6</v>
+        <v/>
       </c>
     </row>
     <row r="22" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1736,11 +1763,11 @@
       <c r="E22" s="19"/>
       <c r="F22" s="20">
         <f t="shared" ref="F22:G22" si="3">SUM(COUNTIF(F10:F21,TRUE))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G22" s="20">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H22" s="19"/>
     </row>
@@ -1760,20 +1787,20 @@
       <c r="E23" s="19"/>
       <c r="F23" s="33">
         <f>F22/$A$21*100</f>
-        <v>33.333333333333329</v>
+        <v>41.666666666666671</v>
       </c>
       <c r="G23" s="33">
         <f>G22/$A$21*100</f>
-        <v>33.333333333333329</v>
+        <v>41.666666666666671</v>
       </c>
       <c r="H23" s="19"/>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C25" s="37" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F25" s="38" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
@@ -1807,23 +1834,13 @@
     <mergeCell ref="H8:H9"/>
     <mergeCell ref="F5:G5"/>
   </mergeCells>
-  <conditionalFormatting sqref="D10:D21">
-    <cfRule type="cellIs" dxfId="11" priority="33" operator="equal">
+  <conditionalFormatting sqref="C10:D21">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G10:G21">
-    <cfRule type="cellIs" dxfId="10" priority="21" operator="equal">
-      <formula>FALSE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F10:F21">
-    <cfRule type="cellIs" dxfId="9" priority="2" operator="equal">
-      <formula>FALSE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C10:C21">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+  <conditionalFormatting sqref="F10:G21">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2170,7 +2187,7 @@
     <mergeCell ref="E8:E9"/>
   </mergeCells>
   <conditionalFormatting sqref="C10:D21">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>
